--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>50.0264</v>
+        <v>63.9574</v>
       </c>
       <c r="E2" t="n">
-        <v>40.3685</v>
+        <v>45.938</v>
       </c>
       <c r="F2" t="n">
-        <v>9.6579</v>
+        <v>18.0198</v>
       </c>
       <c r="G2" t="n">
-        <v>22.6633</v>
+        <v>30.9978</v>
       </c>
       <c r="H2" t="n">
-        <v>16.2262</v>
+        <v>21.1557</v>
       </c>
       <c r="I2" t="n">
-        <v>6.436999999999999</v>
+        <v>9.8421</v>
       </c>
       <c r="J2" t="n">
-        <v>38.7018</v>
+        <v>48.4426</v>
       </c>
       <c r="K2" t="n">
-        <v>23.3156</v>
+        <v>31.1761</v>
       </c>
       <c r="L2" t="n">
-        <v>15.3864</v>
+        <v>17.2667</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.0384</v>
+        <v>-17.4447</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.0894</v>
+        <v>-10.0203</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.949200000000001</v>
+        <v>-7.424700000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.165899999999999</v>
+        <v>-9.3329</v>
       </c>
       <c r="Q2" t="n">
-        <v>-41.0569</v>
+        <v>-51.9001</v>
       </c>
       <c r="R2" t="n">
-        <v>32.8907</v>
+        <v>42.5672</v>
       </c>
       <c r="S2" t="n">
-        <v>-8.434899999999999</v>
+        <v>-12.0384</v>
       </c>
       <c r="T2" t="n">
-        <v>-8.824999999999999</v>
+        <v>-12.6483</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3901000000000001</v>
+        <v>0.6100999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>43.964</v>
+        <v>54.3306</v>
       </c>
       <c r="W2" t="n">
-        <v>51.5487</v>
+        <v>62.0432</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.5846</v>
+        <v>-7.7128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>40.0073</v>
+        <v>57.727</v>
       </c>
       <c r="E3" t="n">
-        <v>30.3928</v>
+        <v>46.6814</v>
       </c>
       <c r="F3" t="n">
-        <v>9.614700000000001</v>
+        <v>11.0456</v>
       </c>
       <c r="G3" t="n">
-        <v>13.6487</v>
+        <v>31.7575</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1496</v>
+        <v>16.1748</v>
       </c>
       <c r="I3" t="n">
-        <v>12.4989</v>
+        <v>15.5825</v>
       </c>
       <c r="J3" t="n">
-        <v>26.9397</v>
+        <v>46.3307</v>
       </c>
       <c r="K3" t="n">
-        <v>12.1825</v>
+        <v>28.0947</v>
       </c>
       <c r="L3" t="n">
-        <v>14.7571</v>
+        <v>18.236</v>
       </c>
       <c r="M3" t="n">
-        <v>-13.2912</v>
+        <v>-14.5734</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.033</v>
+        <v>-11.9196</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.2579</v>
+        <v>-2.6534</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.5367</v>
+        <v>11.154</v>
       </c>
       <c r="Q3" t="n">
-        <v>-49.2229</v>
+        <v>-39.6084</v>
       </c>
       <c r="R3" t="n">
-        <v>44.686</v>
+        <v>50.7621</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.6844</v>
+        <v>17.5539</v>
       </c>
       <c r="T3" t="n">
-        <v>-7.1646</v>
+        <v>12.0606</v>
       </c>
       <c r="U3" t="n">
-        <v>3.48</v>
+        <v>5.4935</v>
       </c>
       <c r="V3" t="n">
-        <v>34.5798</v>
+        <v>-2.7384</v>
       </c>
       <c r="W3" t="n">
-        <v>59.8402</v>
+        <v>27.8974</v>
       </c>
       <c r="X3" t="n">
-        <v>-25.2602</v>
+        <v>-30.6361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>34.9228</v>
+        <v>55.56659999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>30.426</v>
+        <v>43.398</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4973</v>
+        <v>12.1686</v>
       </c>
       <c r="G4" t="n">
-        <v>16.4819</v>
+        <v>18.7125</v>
       </c>
       <c r="H4" t="n">
-        <v>14.6348</v>
+        <v>6.0648</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8475</v>
+        <v>12.6474</v>
       </c>
       <c r="J4" t="n">
-        <v>32.2008</v>
+        <v>35.9249</v>
       </c>
       <c r="K4" t="n">
-        <v>25.3974</v>
+        <v>20.8583</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8034</v>
+        <v>15.0664</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.7187</v>
+        <v>-17.2124</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.7626</v>
+        <v>-14.7933</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.9559</v>
+        <v>-2.4191</v>
       </c>
       <c r="P4" t="n">
-        <v>4.7635</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.974</v>
+        <v>-57.3636</v>
       </c>
       <c r="R4" t="n">
-        <v>41.7373</v>
+        <v>55.0868</v>
       </c>
       <c r="S4" t="n">
-        <v>16.6662</v>
+        <v>-6.8564</v>
       </c>
       <c r="T4" t="n">
-        <v>12.4124</v>
+        <v>-8.5038</v>
       </c>
       <c r="U4" t="n">
-        <v>4.2536</v>
+        <v>1.6469</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.9889</v>
+        <v>45.9868</v>
       </c>
       <c r="W4" t="n">
-        <v>22.786</v>
+        <v>73.3399</v>
       </c>
       <c r="X4" t="n">
-        <v>-25.7746</v>
+        <v>-27.3529</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>17.9262</v>
+        <v>23.1704</v>
       </c>
       <c r="E5" t="n">
-        <v>10.1966</v>
+        <v>15.4476</v>
       </c>
       <c r="F5" t="n">
-        <v>7.7296</v>
+        <v>7.722900000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>6.177200000000001</v>
+        <v>12.9358</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3366</v>
+        <v>0.1033999999999996</v>
       </c>
       <c r="I5" t="n">
-        <v>5.840400000000001</v>
+        <v>12.8321</v>
       </c>
       <c r="J5" t="n">
-        <v>19.3185</v>
+        <v>26.4484</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5233</v>
+        <v>6.8597</v>
       </c>
       <c r="L5" t="n">
-        <v>14.7954</v>
+        <v>19.5886</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.1411</v>
+        <v>-13.5129</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.1865</v>
+        <v>-6.7558</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.954600000000001</v>
+        <v>-6.7569</v>
       </c>
       <c r="P5" t="n">
-        <v>7.4855</v>
+        <v>12.2922</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.0125</v>
+        <v>-19.3489</v>
       </c>
       <c r="R5" t="n">
-        <v>24.4982</v>
+        <v>31.6411</v>
       </c>
       <c r="S5" t="n">
-        <v>7.5413</v>
+        <v>3.934699999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>6.155099999999999</v>
+        <v>5.3803</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3864</v>
+        <v>-1.4455</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.278</v>
+        <v>-5.9921</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7356</v>
+        <v>2.967899999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.013500000000001</v>
+        <v>-8.960000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>13.1377</v>
+        <v>17.3444</v>
       </c>
       <c r="E6" t="n">
-        <v>6.4333</v>
+        <v>6.711</v>
       </c>
       <c r="F6" t="n">
-        <v>6.704599999999999</v>
+        <v>10.6336</v>
       </c>
       <c r="G6" t="n">
-        <v>4.498699999999999</v>
+        <v>10.6183</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6426</v>
+        <v>4.521400000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1438999999999999</v>
+        <v>6.0968</v>
       </c>
       <c r="J6" t="n">
-        <v>5.639699999999999</v>
+        <v>25.1899</v>
       </c>
       <c r="K6" t="n">
-        <v>7.5807</v>
+        <v>15.0792</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9411</v>
+        <v>10.1109</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1411</v>
+        <v>-14.5719</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.9381</v>
+        <v>-10.5583</v>
       </c>
       <c r="O6" t="n">
-        <v>1.797</v>
+        <v>-4.0142</v>
       </c>
       <c r="P6" t="n">
-        <v>4.9902</v>
+        <v>12.9749</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3098</v>
+        <v>-22.0806</v>
       </c>
       <c r="R6" t="n">
-        <v>9.3002</v>
+        <v>35.0554</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9702</v>
+        <v>-2.7363</v>
       </c>
       <c r="T6" t="n">
-        <v>2.211</v>
+        <v>-3.811</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7592</v>
+        <v>1.0747</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3214</v>
+        <v>-3.5125</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8924</v>
+        <v>7.412199999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.2139</v>
+        <v>-10.9246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>12.9943</v>
+        <v>16.4161</v>
       </c>
       <c r="E7" t="n">
-        <v>7.9071</v>
+        <v>6.215899999999996</v>
       </c>
       <c r="F7" t="n">
-        <v>5.0872</v>
+        <v>10.2002</v>
       </c>
       <c r="G7" t="n">
-        <v>9.850299999999999</v>
+        <v>15.6239</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5166</v>
+        <v>-3.963000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>7.3338</v>
+        <v>19.5871</v>
       </c>
       <c r="J7" t="n">
-        <v>18.7796</v>
+        <v>38.6192</v>
       </c>
       <c r="K7" t="n">
-        <v>7.811</v>
+        <v>10.0946</v>
       </c>
       <c r="L7" t="n">
-        <v>10.9685</v>
+        <v>28.5246</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.929399999999999</v>
+        <v>-22.9954</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.2946</v>
+        <v>-14.0578</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.6346</v>
+        <v>-8.937199999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.1758</v>
+        <v>5.463</v>
       </c>
       <c r="Q7" t="n">
-        <v>-24.7248</v>
+        <v>-43.7057</v>
       </c>
       <c r="R7" t="n">
-        <v>21.5492</v>
+        <v>49.1686</v>
       </c>
       <c r="S7" t="n">
-        <v>15.5435</v>
+        <v>-10.3623</v>
       </c>
       <c r="T7" t="n">
-        <v>6.7175</v>
+        <v>-12.38</v>
       </c>
       <c r="U7" t="n">
-        <v>8.8261</v>
+        <v>2.0181</v>
       </c>
       <c r="V7" t="n">
-        <v>-9.223599999999999</v>
+        <v>5.6915</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1346</v>
+        <v>23.6825</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.3583</v>
+        <v>-17.9911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>10.8264</v>
+        <v>13.265</v>
       </c>
       <c r="E8" t="n">
-        <v>6.4072</v>
+        <v>7.6888</v>
       </c>
       <c r="F8" t="n">
-        <v>4.419200000000001</v>
+        <v>5.576600000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7535</v>
+        <v>10.0477</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7398</v>
+        <v>2.611200000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0138</v>
+        <v>7.4361</v>
       </c>
       <c r="J8" t="n">
-        <v>25.364</v>
+        <v>18.6322</v>
       </c>
       <c r="K8" t="n">
-        <v>13.8547</v>
+        <v>7.692</v>
       </c>
       <c r="L8" t="n">
-        <v>11.509</v>
+        <v>10.9399</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.6107</v>
+        <v>-8.5847</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.115</v>
+        <v>-5.081</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.4955</v>
+        <v>-3.5037</v>
       </c>
       <c r="P8" t="n">
-        <v>7.7122</v>
+        <v>-3.187</v>
       </c>
       <c r="Q8" t="n">
-        <v>-20.6421</v>
+        <v>-24.8119</v>
       </c>
       <c r="R8" t="n">
-        <v>28.3542</v>
+        <v>21.6252</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.3043</v>
+        <v>15.5936</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.8108</v>
+        <v>6.7721</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5065</v>
+        <v>8.8216</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.335199999999999</v>
+        <v>-9.1891</v>
       </c>
       <c r="W8" t="n">
-        <v>5.4957</v>
+        <v>7.0966</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.8309</v>
+        <v>-16.2857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2245</v>
+        <v>12.0038</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9713</v>
+        <v>21.7167</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2533</v>
+        <v>-9.7126</v>
       </c>
       <c r="G9" t="n">
-        <v>6.316</v>
+        <v>47.7975</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09480000000000155</v>
+        <v>15.5628</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2211</v>
+        <v>32.2342</v>
       </c>
       <c r="J9" t="n">
-        <v>22.0961</v>
+        <v>63.303</v>
       </c>
       <c r="K9" t="n">
-        <v>4.721100000000001</v>
+        <v>31.0685</v>
       </c>
       <c r="L9" t="n">
-        <v>17.3751</v>
+        <v>32.235</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.7804</v>
+        <v>-15.5058</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.6263</v>
+        <v>-15.5053</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.1537</v>
+        <v>-0.0006000000000000727</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.495099999999999</v>
+        <v>-10.9262</v>
       </c>
       <c r="Q9" t="n">
-        <v>-33.7983</v>
+        <v>-49.6239</v>
       </c>
       <c r="R9" t="n">
-        <v>31.303</v>
+        <v>38.6975</v>
       </c>
       <c r="S9" t="n">
-        <v>12.2695</v>
+        <v>-22.5304</v>
       </c>
       <c r="T9" t="n">
-        <v>6.8384</v>
+        <v>-15.8035</v>
       </c>
       <c r="U9" t="n">
-        <v>5.431</v>
+        <v>-6.727</v>
       </c>
       <c r="V9" t="n">
-        <v>-9.8658</v>
+        <v>-2.3368</v>
       </c>
       <c r="W9" t="n">
-        <v>9.8347</v>
+        <v>23.8404</v>
       </c>
       <c r="X9" t="n">
-        <v>-19.7005</v>
+        <v>-26.1774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SAMANIC</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>5.3413</v>
+        <v>11.59</v>
       </c>
       <c r="E10" t="n">
-        <v>8.172800000000001</v>
+        <v>1.9934</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8315</v>
+        <v>9.5966</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4194</v>
+        <v>1.8139</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1644</v>
+        <v>1.3441</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5837000000000001</v>
+        <v>0.4698</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1837</v>
+        <v>4.0445</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7493</v>
+        <v>5.5451</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4342</v>
+        <v>-1.5006</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.603</v>
+        <v>-2.2307</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.585</v>
+        <v>-4.2009</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.018</v>
+        <v>1.9702</v>
       </c>
       <c r="P10" t="n">
-        <v>1.361</v>
+        <v>5.6908</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4951</v>
+        <v>-7.0565</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8562</v>
+        <v>12.7475</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2924</v>
+        <v>4.7878</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0605</v>
+        <v>1.8083</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3530000000000001</v>
+        <v>2.9793</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6921</v>
+        <v>-0.7025999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>7.4238</v>
+        <v>3.1971</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7317</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>3.000599999999999</v>
+        <v>5.703600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1983</v>
+        <v>-2.909099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>6.198500000000001</v>
+        <v>8.613399999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.8023</v>
+        <v>-10.2145</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.421799999999999</v>
+        <v>-12.4272</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3807</v>
+        <v>2.212799999999998</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.310699999999999</v>
+        <v>-3.834899999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.7141</v>
+        <v>-6.7215</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4032999999999993</v>
+        <v>2.8869</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.4917</v>
+        <v>-6.3797</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.7076</v>
+        <v>-5.7055</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.7839</v>
+        <v>-0.6739999999999998</v>
       </c>
       <c r="P11" t="n">
-        <v>17.693</v>
+        <v>20.7146</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.1661</v>
+        <v>-8.422499999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>25.8589</v>
+        <v>29.1369</v>
       </c>
       <c r="S11" t="n">
-        <v>6.298</v>
+        <v>6.9742</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6792</v>
+        <v>4.6747</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6185</v>
+        <v>2.2994</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.1879</v>
+        <v>-11.7699</v>
       </c>
       <c r="W11" t="n">
-        <v>3.5995</v>
+        <v>4.6735</v>
       </c>
       <c r="X11" t="n">
-        <v>-13.7874</v>
+        <v>-16.4434</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>L. SAMANIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5171</v>
+        <v>5.3309</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2982</v>
+        <v>8.082000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7810999999999999</v>
+        <v>-2.7511</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1478</v>
+        <v>-0.4136</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0779</v>
+        <v>0.1719</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2257</v>
+        <v>-0.5854</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9707</v>
+        <v>3.1244</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6451</v>
+        <v>2.716</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6744</v>
+        <v>0.4085</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1185</v>
+        <v>-3.5381</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5672</v>
+        <v>-2.544</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5513</v>
+        <v>-0.994</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1341</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>3.8698</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0402</v>
+        <v>-0.2947</v>
       </c>
       <c r="T12" t="n">
-        <v>0.369</v>
+        <v>0.06429999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4092</v>
+        <v>-0.3591</v>
       </c>
       <c r="V12" t="n">
-        <v>2.571</v>
+        <v>4.673399999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1854</v>
+        <v>7.3971</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3856</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2.190999999999999</v>
+        <v>2.5176</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9086</v>
+        <v>3.2823</v>
       </c>
       <c r="F13" t="n">
-        <v>7.0997</v>
+        <v>-0.7647</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6135000000000005</v>
+        <v>-1.1468</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.798500000000001</v>
+        <v>1.0771</v>
       </c>
       <c r="I13" t="n">
-        <v>10.4121</v>
+        <v>-2.2239</v>
       </c>
       <c r="J13" t="n">
-        <v>21.9862</v>
+        <v>0.9595</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5297</v>
+        <v>1.6375</v>
       </c>
       <c r="L13" t="n">
-        <v>20.4567</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.3727</v>
+        <v>-2.1064</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.3284</v>
+        <v>-0.5605</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.0442</v>
+        <v>-1.546</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1754</v>
+        <v>1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-37.2009</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>40.3762</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.7724</v>
+        <v>-0.0396</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.169600000000001</v>
+        <v>0.3714</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3973</v>
+        <v>-0.4111</v>
       </c>
       <c r="V13" t="n">
-        <v>5.174399999999999</v>
+        <v>2.5659</v>
       </c>
       <c r="W13" t="n">
-        <v>19.4756</v>
+        <v>2.179</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.3013</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2311999999999994</v>
+        <v>2.379300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>10.2072</v>
+        <v>4.071400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.976000000000001</v>
+        <v>-1.6921</v>
       </c>
       <c r="G14" t="n">
-        <v>34.5342</v>
+        <v>-6.805099999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>10.5876</v>
+        <v>-5.6492</v>
       </c>
       <c r="I14" t="n">
-        <v>23.9467</v>
+        <v>-1.1558</v>
       </c>
       <c r="J14" t="n">
-        <v>45.4343</v>
+        <v>3.1747</v>
       </c>
       <c r="K14" t="n">
-        <v>21.0256</v>
+        <v>-0.02760000000000007</v>
       </c>
       <c r="L14" t="n">
-        <v>24.409</v>
+        <v>3.2025</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.9005</v>
+        <v>-9.98</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.4379</v>
+        <v>-5.6215</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4622999999999997</v>
+        <v>-4.3584</v>
       </c>
       <c r="P14" t="n">
-        <v>-11.3415</v>
+        <v>-0.6828000000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-39.9225</v>
+        <v>-13.2029</v>
       </c>
       <c r="R14" t="n">
-        <v>28.581</v>
+        <v>12.5197</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.8588</v>
+        <v>13.5943</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.4381</v>
+        <v>10.4857</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.4209</v>
+        <v>3.1086</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.1023</v>
+        <v>-3.7268</v>
       </c>
       <c r="W14" t="n">
-        <v>16.1334</v>
+        <v>3.6138</v>
       </c>
       <c r="X14" t="n">
-        <v>-23.2356</v>
+        <v>-7.3406</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2052</v>
+        <v>-1.7387</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3582000000000001</v>
+        <v>1.1571</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8470999999999996</v>
+        <v>-2.8958</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.095000000000001</v>
+        <v>0.2558</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.6507</v>
+        <v>1.4935</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4444</v>
+        <v>-1.2378</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6544</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7636999999999999</v>
+        <v>1.379</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4181</v>
+        <v>-0.7524</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.749499999999999</v>
+        <v>-0.3707</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.887</v>
+        <v>0.1146</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.8625</v>
+        <v>-0.4854</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>0.4552</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.124700000000001</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>7.258500000000001</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8445</v>
+        <v>0.274</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7977</v>
+        <v>0.4411</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0468</v>
+        <v>-0.1671</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0888</v>
+        <v>-2.7237</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3143</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.4032</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4803</v>
+        <v>-2.65</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5760999999999999</v>
+        <v>-4.9022</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0564</v>
+        <v>2.2524</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3201</v>
+        <v>1.015599999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9567</v>
+        <v>-3.1781</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2768</v>
+        <v>4.1936</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0448</v>
+        <v>4.5514</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8312</v>
+        <v>-0.7044999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7864</v>
+        <v>5.2559</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3649</v>
+        <v>-3.5357</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1255</v>
+        <v>-2.4737</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4904</v>
+        <v>-1.062</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-9.5608</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>6.8291</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2519</v>
+        <v>-0.002400000000000263</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4386</v>
+        <v>0.4075</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1866</v>
+        <v>-0.4099000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.639</v>
+        <v>-0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>-0.3006</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>J. MAKER BOL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6467</v>
+        <v>-3.3245</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.7709</v>
+        <v>-1.7342</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1241</v>
+        <v>-1.5904</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0099</v>
+        <v>-3.8355</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.2067</v>
+        <v>-1.7144</v>
       </c>
       <c r="I17" t="n">
-        <v>4.216599999999999</v>
+        <v>-2.1212</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6459</v>
+        <v>-2.3173</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6661000000000001</v>
+        <v>-1.5276</v>
       </c>
       <c r="L17" t="n">
-        <v>5.311900000000001</v>
+        <v>-0.7896</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.6361</v>
+        <v>-1.5184</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.5407</v>
+        <v>-0.1868</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0954</v>
+        <v>-1.3315</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-9.527200000000001</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>6.8051</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.002699999999999883</v>
+        <v>-0.1718</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3993</v>
+        <v>-0.2788</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4019</v>
+        <v>0.107</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2891</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6429</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MAKER BOL</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3223</v>
+        <v>-3.450199999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7195</v>
+        <v>-7.838599999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6028</v>
+        <v>4.388500000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8316</v>
+        <v>0.2919000000000003</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7099</v>
+        <v>-7.008100000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1218</v>
+        <v>7.3</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3071</v>
+        <v>20.4838</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5208</v>
+        <v>2.218100000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7864</v>
+        <v>18.2655</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5244</v>
+        <v>-20.1916</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1891</v>
+        <v>-9.226000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3354</v>
+        <v>-10.9657</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>-3.642099999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-44.3885</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>40.7461</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1712</v>
+        <v>12.4854</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2783</v>
+        <v>6.3736</v>
       </c>
       <c r="U18" t="n">
-        <v>0.107</v>
+        <v>6.1117</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-12.5854</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>9.6922</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-22.2776</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.204800000000001</v>
+        <v>-6.305</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.4348</v>
+        <v>-5.7956</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7701000000000002</v>
+        <v>-0.5094000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.5631</v>
+        <v>-4.6488</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.973599999999999</v>
+        <v>-5.0724</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4106000000000001</v>
+        <v>0.4237000000000003</v>
       </c>
       <c r="J19" t="n">
-        <v>5.0383</v>
+        <v>4.7668</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4581</v>
+        <v>3.2347</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5804</v>
+        <v>1.5323</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.6013</v>
+        <v>-9.415700000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-8.431800000000001</v>
+        <v>-8.3071</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1696</v>
+        <v>-1.1086</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.444</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q19" t="n">
-        <v>-17.9199</v>
+        <v>-17.983</v>
       </c>
       <c r="R19" t="n">
-        <v>12.4759</v>
+        <v>12.5197</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1842</v>
+        <v>5.1971</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9225999999999999</v>
+        <v>0.9402</v>
       </c>
       <c r="U19" t="n">
-        <v>4.2614</v>
+        <v>4.2568</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.381599999999999</v>
+        <v>-1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>6.5243</v>
+        <v>6.4803</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.905799999999999</v>
+        <v>-7.8703</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.6617</v>
+        <v>-8.7334</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.1675</v>
+        <v>-10.4041</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5059</v>
+        <v>1.6706</v>
       </c>
       <c r="G20" t="n">
-        <v>3.174</v>
+        <v>3.127</v>
       </c>
       <c r="H20" t="n">
-        <v>6.996799999999999</v>
+        <v>6.9991</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.8228</v>
+        <v>-3.8722</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5599</v>
+        <v>4.3907</v>
       </c>
       <c r="K20" t="n">
-        <v>8.3111</v>
+        <v>8.238299999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.7512</v>
+        <v>-3.8474</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3859</v>
+        <v>-1.2638</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3142</v>
+        <v>-1.2391</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.07150000000000004</v>
+        <v>-0.02469999999999997</v>
       </c>
       <c r="P20" t="n">
-        <v>-9.754</v>
+        <v>-9.7881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-17.2392</v>
+        <v>-17.3</v>
       </c>
       <c r="R20" t="n">
-        <v>7.4855</v>
+        <v>7.5119</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0352</v>
+        <v>1.0384</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2299</v>
+        <v>0.2398</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8052999999999999</v>
+        <v>0.7986</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.1174</v>
+        <v>-3.1107</v>
       </c>
       <c r="W20" t="n">
-        <v>2.282</v>
+        <v>2.2654</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.3991</v>
+        <v>-5.376</v>
       </c>
     </row>
     <row r="21">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.1208</v>
+        <v>-9.886099999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.811000000000001</v>
+        <v>-1.513199999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.3097</v>
+        <v>-8.3727</v>
       </c>
       <c r="G21" t="n">
-        <v>2.940099999999999</v>
+        <v>4.9092</v>
       </c>
       <c r="H21" t="n">
-        <v>5.489599999999999</v>
+        <v>4.6691</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5494</v>
+        <v>0.2398999999999996</v>
       </c>
       <c r="J21" t="n">
-        <v>13.7332</v>
+        <v>17.9425</v>
       </c>
       <c r="K21" t="n">
-        <v>11.0351</v>
+        <v>11.8183</v>
       </c>
       <c r="L21" t="n">
-        <v>2.698</v>
+        <v>6.1243</v>
       </c>
       <c r="M21" t="n">
-        <v>-10.793</v>
+        <v>-13.0337</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.545500000000001</v>
+        <v>-7.1493</v>
       </c>
       <c r="O21" t="n">
-        <v>-5.2475</v>
+        <v>-5.8843</v>
       </c>
       <c r="P21" t="n">
-        <v>-12.4756</v>
+        <v>-13.6578</v>
       </c>
       <c r="Q21" t="n">
-        <v>-29.9418</v>
+        <v>-32.3237</v>
       </c>
       <c r="R21" t="n">
-        <v>17.4661</v>
+        <v>18.6659</v>
       </c>
       <c r="S21" t="n">
-        <v>-14.4682</v>
+        <v>-15.1427</v>
       </c>
       <c r="T21" t="n">
-        <v>-7.8451</v>
+        <v>-8.463200000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.6231</v>
+        <v>-6.6792</v>
       </c>
       <c r="V21" t="n">
-        <v>13.8833</v>
+        <v>14.0054</v>
       </c>
       <c r="W21" t="n">
-        <v>21.2428</v>
+        <v>21.331</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.3596</v>
+        <v>-7.3258</v>
       </c>
     </row>
     <row r="22">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>-21.1079</v>
+        <v>-11.7622</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.7831</v>
+        <v>-8.168399999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.3248</v>
+        <v>-3.5941</v>
       </c>
       <c r="G22" t="n">
-        <v>3.3421</v>
+        <v>13.9109</v>
       </c>
       <c r="H22" t="n">
-        <v>10.5336</v>
+        <v>14.539</v>
       </c>
       <c r="I22" t="n">
-        <v>-7.1913</v>
+        <v>-0.6281000000000007</v>
       </c>
       <c r="J22" t="n">
-        <v>18.237</v>
+        <v>28.3364</v>
       </c>
       <c r="K22" t="n">
-        <v>20.205</v>
+        <v>25.7289</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9681</v>
+        <v>2.6074</v>
       </c>
       <c r="M22" t="n">
-        <v>-14.895</v>
+        <v>-14.4256</v>
       </c>
       <c r="N22" t="n">
-        <v>-9.6715</v>
+        <v>-11.1894</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.2234</v>
+        <v>-3.2361</v>
       </c>
       <c r="P22" t="n">
-        <v>-20.8686</v>
+        <v>-27.3157</v>
       </c>
       <c r="Q22" t="n">
-        <v>-41.7375</v>
+        <v>-55.7701</v>
       </c>
       <c r="R22" t="n">
-        <v>20.8686</v>
+        <v>28.4539</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2354</v>
+        <v>-1.4677</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3385</v>
+        <v>0.3276000000000002</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8968999999999999</v>
+        <v>-1.7952</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3461</v>
+        <v>3.110300000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>11.0557</v>
+        <v>18.9378</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.4018</v>
+        <v>-15.8271</v>
       </c>
     </row>
     <row r="23">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>144.5971</v>
+        <v>239.122</v>
       </c>
       <c r="E23" t="n">
-        <v>113.2052</v>
+        <v>169.1182</v>
       </c>
       <c r="F23" t="n">
-        <v>31.3925</v>
+        <v>70.0059</v>
       </c>
       <c r="G23" t="n">
-        <v>109.8241</v>
+        <v>176.751</v>
       </c>
       <c r="H23" t="n">
-        <v>47.3864</v>
+        <v>57.4755</v>
       </c>
       <c r="I23" t="n">
-        <v>62.438</v>
+        <v>119.2737</v>
       </c>
       <c r="J23" t="n">
-        <v>301.9108000000001</v>
+        <v>389.1399</v>
       </c>
       <c r="K23" t="n">
-        <v>163.5118</v>
+        <v>204.4578</v>
       </c>
       <c r="L23" t="n">
-        <v>138.3989</v>
+        <v>184.6835</v>
       </c>
       <c r="M23" t="n">
-        <v>-192.0875</v>
+        <v>-212.3913</v>
       </c>
       <c r="N23" t="n">
-        <v>-116.1259</v>
+        <v>-146.9806</v>
       </c>
       <c r="O23" t="n">
-        <v>-75.9598</v>
+        <v>-65.41030000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-30.6228</v>
+        <v>-17.0721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-438.9235</v>
+        <v>-517.8655</v>
       </c>
       <c r="R23" t="n">
-        <v>408.2996000000001</v>
+        <v>500.7912000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>20.3396</v>
+        <v>9.790699999999998</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.638800000000002</v>
+        <v>-11.5414</v>
       </c>
       <c r="U23" t="n">
-        <v>24.97760000000001</v>
+        <v>21.33219999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>45.0566</v>
+        <v>69.65419999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>254.8546</v>
+        <v>309.3809</v>
       </c>
       <c r="X23" t="n">
-        <v>-209.7973</v>
+        <v>-239.7266</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Baskonia.xlsx
@@ -565,13 +565,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>63.9574</v>
+        <v>74.9038</v>
       </c>
       <c r="E2" t="n">
-        <v>45.938</v>
+        <v>55.4</v>
       </c>
       <c r="F2" t="n">
-        <v>18.0198</v>
+        <v>19.5037</v>
       </c>
       <c r="G2" t="n">
         <v>30.9978</v>
@@ -610,13 +610,13 @@
         <v>42.5672</v>
       </c>
       <c r="S2" t="n">
-        <v>-12.0384</v>
+        <v>-1.0918</v>
       </c>
       <c r="T2" t="n">
-        <v>-12.6483</v>
+        <v>-3.1863</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6100999999999999</v>
+        <v>2.0944</v>
       </c>
       <c r="V2" t="n">
         <v>54.3306</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>57.727</v>
+        <v>62.7423</v>
       </c>
       <c r="E3" t="n">
-        <v>46.6814</v>
+        <v>49.1813</v>
       </c>
       <c r="F3" t="n">
-        <v>11.0456</v>
+        <v>13.5608</v>
       </c>
       <c r="G3" t="n">
-        <v>31.7575</v>
+        <v>18.7125</v>
       </c>
       <c r="H3" t="n">
-        <v>16.1748</v>
+        <v>6.0648</v>
       </c>
       <c r="I3" t="n">
-        <v>15.5825</v>
+        <v>12.6474</v>
       </c>
       <c r="J3" t="n">
-        <v>46.3307</v>
+        <v>35.9249</v>
       </c>
       <c r="K3" t="n">
-        <v>28.0947</v>
+        <v>20.8583</v>
       </c>
       <c r="L3" t="n">
-        <v>18.236</v>
+        <v>15.0664</v>
       </c>
       <c r="M3" t="n">
-        <v>-14.5734</v>
+        <v>-17.2124</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.9196</v>
+        <v>-14.7933</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.6534</v>
+        <v>-2.4191</v>
       </c>
       <c r="P3" t="n">
-        <v>11.154</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q3" t="n">
-        <v>-39.6084</v>
+        <v>-57.3636</v>
       </c>
       <c r="R3" t="n">
-        <v>50.7621</v>
+        <v>55.0868</v>
       </c>
       <c r="S3" t="n">
-        <v>17.5539</v>
+        <v>0.319</v>
       </c>
       <c r="T3" t="n">
-        <v>12.0606</v>
+        <v>-2.7204</v>
       </c>
       <c r="U3" t="n">
-        <v>5.4935</v>
+        <v>3.0393</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.7384</v>
+        <v>45.9868</v>
       </c>
       <c r="W3" t="n">
-        <v>27.8974</v>
+        <v>73.3399</v>
       </c>
       <c r="X3" t="n">
-        <v>-30.6361</v>
+        <v>-27.3529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>55.56659999999999</v>
+        <v>46.0485</v>
       </c>
       <c r="E4" t="n">
-        <v>43.398</v>
+        <v>36.7601</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1686</v>
+        <v>9.288600000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>18.7125</v>
+        <v>31.7575</v>
       </c>
       <c r="H4" t="n">
-        <v>6.0648</v>
+        <v>16.1748</v>
       </c>
       <c r="I4" t="n">
-        <v>12.6474</v>
+        <v>15.5825</v>
       </c>
       <c r="J4" t="n">
-        <v>35.9249</v>
+        <v>46.3307</v>
       </c>
       <c r="K4" t="n">
-        <v>20.8583</v>
+        <v>28.0947</v>
       </c>
       <c r="L4" t="n">
-        <v>15.0664</v>
+        <v>18.236</v>
       </c>
       <c r="M4" t="n">
-        <v>-17.2124</v>
+        <v>-14.5734</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.7933</v>
+        <v>-11.9196</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4191</v>
+        <v>-2.6534</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2762</v>
+        <v>11.154</v>
       </c>
       <c r="Q4" t="n">
-        <v>-57.3636</v>
+        <v>-39.6084</v>
       </c>
       <c r="R4" t="n">
-        <v>55.0868</v>
+        <v>50.7621</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.8564</v>
+        <v>5.8758</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.5038</v>
+        <v>2.1395</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6469</v>
+        <v>3.7365</v>
       </c>
       <c r="V4" t="n">
-        <v>45.9868</v>
+        <v>-2.7384</v>
       </c>
       <c r="W4" t="n">
-        <v>73.3399</v>
+        <v>27.8974</v>
       </c>
       <c r="X4" t="n">
-        <v>-27.3529</v>
+        <v>-30.6361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>23.1704</v>
+        <v>27.3789</v>
       </c>
       <c r="E5" t="n">
-        <v>15.4476</v>
+        <v>14.6611</v>
       </c>
       <c r="F5" t="n">
-        <v>7.722900000000001</v>
+        <v>12.7181</v>
       </c>
       <c r="G5" t="n">
-        <v>12.9358</v>
+        <v>15.6239</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1033999999999996</v>
+        <v>-3.963000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>12.8321</v>
+        <v>19.5871</v>
       </c>
       <c r="J5" t="n">
-        <v>26.4484</v>
+        <v>38.6192</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8597</v>
+        <v>10.0946</v>
       </c>
       <c r="L5" t="n">
-        <v>19.5886</v>
+        <v>28.5246</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.5129</v>
+        <v>-22.9954</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.7558</v>
+        <v>-14.0578</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.7569</v>
+        <v>-8.937199999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>12.2922</v>
+        <v>5.463</v>
       </c>
       <c r="Q5" t="n">
-        <v>-19.3489</v>
+        <v>-43.7057</v>
       </c>
       <c r="R5" t="n">
-        <v>31.6411</v>
+        <v>49.1686</v>
       </c>
       <c r="S5" t="n">
-        <v>3.934699999999999</v>
+        <v>0.6008000000000002</v>
       </c>
       <c r="T5" t="n">
-        <v>5.3803</v>
+        <v>-3.9354</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4455</v>
+        <v>4.5364</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.9921</v>
+        <v>5.6915</v>
       </c>
       <c r="W5" t="n">
-        <v>2.967899999999999</v>
+        <v>23.6825</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.960000000000001</v>
+        <v>-17.9911</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>17.3444</v>
+        <v>26.375</v>
       </c>
       <c r="E6" t="n">
-        <v>6.711</v>
+        <v>31.5967</v>
       </c>
       <c r="F6" t="n">
-        <v>10.6336</v>
+        <v>-5.2218</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6183</v>
+        <v>47.7975</v>
       </c>
       <c r="H6" t="n">
-        <v>4.521400000000001</v>
+        <v>15.5628</v>
       </c>
       <c r="I6" t="n">
-        <v>6.0968</v>
+        <v>32.2342</v>
       </c>
       <c r="J6" t="n">
-        <v>25.1899</v>
+        <v>63.303</v>
       </c>
       <c r="K6" t="n">
-        <v>15.0792</v>
+        <v>31.0685</v>
       </c>
       <c r="L6" t="n">
-        <v>10.1109</v>
+        <v>32.235</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.5719</v>
+        <v>-15.5058</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.5583</v>
+        <v>-15.5053</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.0142</v>
+        <v>-0.0006000000000000727</v>
       </c>
       <c r="P6" t="n">
-        <v>12.9749</v>
+        <v>-10.9262</v>
       </c>
       <c r="Q6" t="n">
-        <v>-22.0806</v>
+        <v>-49.6239</v>
       </c>
       <c r="R6" t="n">
-        <v>35.0554</v>
+        <v>38.6975</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.7363</v>
+        <v>-8.1594</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.811</v>
+        <v>-5.9234</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0747</v>
+        <v>-2.2361</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.5125</v>
+        <v>-2.3368</v>
       </c>
       <c r="W6" t="n">
-        <v>7.412199999999999</v>
+        <v>23.8404</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.9246</v>
+        <v>-26.1774</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>16.4161</v>
+        <v>23.5119</v>
       </c>
       <c r="E7" t="n">
-        <v>6.215899999999996</v>
+        <v>9.518699999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>10.2002</v>
+        <v>13.9931</v>
       </c>
       <c r="G7" t="n">
-        <v>15.6239</v>
+        <v>10.6183</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.963000000000001</v>
+        <v>4.521400000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>19.5871</v>
+        <v>6.0968</v>
       </c>
       <c r="J7" t="n">
-        <v>38.6192</v>
+        <v>25.1899</v>
       </c>
       <c r="K7" t="n">
-        <v>10.0946</v>
+        <v>15.0792</v>
       </c>
       <c r="L7" t="n">
-        <v>28.5246</v>
+        <v>10.1109</v>
       </c>
       <c r="M7" t="n">
-        <v>-22.9954</v>
+        <v>-14.5719</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.0578</v>
+        <v>-10.5583</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.937199999999999</v>
+        <v>-4.0142</v>
       </c>
       <c r="P7" t="n">
-        <v>5.463</v>
+        <v>12.9749</v>
       </c>
       <c r="Q7" t="n">
-        <v>-43.7057</v>
+        <v>-22.0806</v>
       </c>
       <c r="R7" t="n">
-        <v>49.1686</v>
+        <v>35.0554</v>
       </c>
       <c r="S7" t="n">
-        <v>-10.3623</v>
+        <v>3.4312</v>
       </c>
       <c r="T7" t="n">
-        <v>-12.38</v>
+        <v>-1.0033</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0181</v>
+        <v>4.434</v>
       </c>
       <c r="V7" t="n">
-        <v>5.6915</v>
+        <v>-3.5125</v>
       </c>
       <c r="W7" t="n">
-        <v>23.6825</v>
+        <v>7.412199999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.9911</v>
+        <v>-10.9246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>13.265</v>
+        <v>22.3138</v>
       </c>
       <c r="E8" t="n">
-        <v>7.6888</v>
+        <v>12.4519</v>
       </c>
       <c r="F8" t="n">
-        <v>5.576600000000001</v>
+        <v>9.861899999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>10.0477</v>
+        <v>12.9358</v>
       </c>
       <c r="H8" t="n">
-        <v>2.611200000000001</v>
+        <v>0.1033999999999996</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4361</v>
+        <v>12.8321</v>
       </c>
       <c r="J8" t="n">
-        <v>18.6322</v>
+        <v>26.4484</v>
       </c>
       <c r="K8" t="n">
-        <v>7.692</v>
+        <v>6.8597</v>
       </c>
       <c r="L8" t="n">
-        <v>10.9399</v>
+        <v>19.5886</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.5847</v>
+        <v>-13.5129</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.081</v>
+        <v>-6.7558</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.5037</v>
+        <v>-6.7569</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.187</v>
+        <v>12.2922</v>
       </c>
       <c r="Q8" t="n">
-        <v>-24.8119</v>
+        <v>-19.3489</v>
       </c>
       <c r="R8" t="n">
-        <v>21.6252</v>
+        <v>31.6411</v>
       </c>
       <c r="S8" t="n">
-        <v>15.5936</v>
+        <v>3.0783</v>
       </c>
       <c r="T8" t="n">
-        <v>6.7721</v>
+        <v>2.3843</v>
       </c>
       <c r="U8" t="n">
-        <v>8.8216</v>
+        <v>0.6937000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>-9.1891</v>
+        <v>-5.9921</v>
       </c>
       <c r="W8" t="n">
-        <v>7.0966</v>
+        <v>2.967899999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.2857</v>
+        <v>-8.960000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12.0038</v>
+        <v>9.8306</v>
       </c>
       <c r="E9" t="n">
-        <v>21.7167</v>
+        <v>0.5443999999999996</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.7126</v>
+        <v>9.286199999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>47.7975</v>
+        <v>1.8139</v>
       </c>
       <c r="H9" t="n">
-        <v>15.5628</v>
+        <v>1.3441</v>
       </c>
       <c r="I9" t="n">
-        <v>32.2342</v>
+        <v>0.4698</v>
       </c>
       <c r="J9" t="n">
-        <v>63.303</v>
+        <v>4.0445</v>
       </c>
       <c r="K9" t="n">
-        <v>31.0685</v>
+        <v>5.5451</v>
       </c>
       <c r="L9" t="n">
-        <v>32.235</v>
+        <v>-1.5006</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.5058</v>
+        <v>-2.2307</v>
       </c>
       <c r="N9" t="n">
-        <v>-15.5053</v>
+        <v>-4.2009</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0006000000000000727</v>
+        <v>1.9702</v>
       </c>
       <c r="P9" t="n">
-        <v>-10.9262</v>
+        <v>5.6908</v>
       </c>
       <c r="Q9" t="n">
-        <v>-49.6239</v>
+        <v>-7.0565</v>
       </c>
       <c r="R9" t="n">
-        <v>38.6975</v>
+        <v>12.7475</v>
       </c>
       <c r="S9" t="n">
-        <v>-22.5304</v>
+        <v>3.0283</v>
       </c>
       <c r="T9" t="n">
-        <v>-15.8035</v>
+        <v>0.3591999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.727</v>
+        <v>2.6689</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3368</v>
+        <v>-0.7025999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>23.8404</v>
+        <v>3.1971</v>
       </c>
       <c r="X9" t="n">
-        <v>-26.1774</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>L. SAMANIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>11.59</v>
+        <v>5.5829</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9934</v>
+        <v>8.270099999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>9.5966</v>
+        <v>-2.6872</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8139</v>
+        <v>-0.4136</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3441</v>
+        <v>0.1719</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4698</v>
+        <v>-0.5854</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0445</v>
+        <v>3.1244</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5451</v>
+        <v>2.716</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5006</v>
+        <v>0.4085</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2307</v>
+        <v>-3.5381</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.2009</v>
+        <v>-2.544</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9702</v>
+        <v>-0.994</v>
       </c>
       <c r="P10" t="n">
-        <v>5.6908</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.0565</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>12.7475</v>
+        <v>3.8698</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7878</v>
+        <v>-0.0428</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8083</v>
+        <v>0.2524</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9793</v>
+        <v>-0.2953</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7025999999999999</v>
+        <v>4.673399999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.1971</v>
+        <v>7.3971</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.8995</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>5.703600000000001</v>
+        <v>5.4594</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.909099999999999</v>
+        <v>2.7977</v>
       </c>
       <c r="F11" t="n">
-        <v>8.613399999999999</v>
+        <v>2.661500000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.2145</v>
+        <v>10.0477</v>
       </c>
       <c r="H11" t="n">
-        <v>-12.4272</v>
+        <v>2.611200000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2.212799999999998</v>
+        <v>7.4361</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.834899999999999</v>
+        <v>18.6322</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.7215</v>
+        <v>7.692</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8869</v>
+        <v>10.9399</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.3797</v>
+        <v>-8.5847</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.7055</v>
+        <v>-5.081</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6739999999999998</v>
+        <v>-3.5037</v>
       </c>
       <c r="P11" t="n">
-        <v>20.7146</v>
+        <v>-3.187</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.422499999999999</v>
+        <v>-24.8119</v>
       </c>
       <c r="R11" t="n">
-        <v>29.1369</v>
+        <v>21.6252</v>
       </c>
       <c r="S11" t="n">
-        <v>6.9742</v>
+        <v>7.787999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6747</v>
+        <v>1.881</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2994</v>
+        <v>5.9071</v>
       </c>
       <c r="V11" t="n">
-        <v>-11.7699</v>
+        <v>-9.1891</v>
       </c>
       <c r="W11" t="n">
-        <v>4.6735</v>
+        <v>7.0966</v>
       </c>
       <c r="X11" t="n">
-        <v>-16.4434</v>
+        <v>-16.2857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SAMANIC</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3309</v>
+        <v>2.888099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.082000000000001</v>
+        <v>6.1091</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7511</v>
+        <v>-3.220899999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4136</v>
+        <v>4.9092</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1719</v>
+        <v>4.6691</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5854</v>
+        <v>0.2398999999999996</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1244</v>
+        <v>17.9425</v>
       </c>
       <c r="K12" t="n">
-        <v>2.716</v>
+        <v>11.8183</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4085</v>
+        <v>6.1243</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5381</v>
+        <v>-13.0337</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.544</v>
+        <v>-7.1493</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.994</v>
+        <v>-5.8843</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3658</v>
+        <v>-13.6578</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.5039</v>
+        <v>-32.3237</v>
       </c>
       <c r="R12" t="n">
-        <v>3.8698</v>
+        <v>18.6659</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2947</v>
+        <v>-2.3683</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06429999999999997</v>
+        <v>-0.8408</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3591</v>
+        <v>-1.5275</v>
       </c>
       <c r="V12" t="n">
-        <v>4.673399999999999</v>
+        <v>14.0054</v>
       </c>
       <c r="W12" t="n">
-        <v>7.3971</v>
+        <v>21.331</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7237</v>
+        <v>-7.3258</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5176</v>
+        <v>2.3748</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2823</v>
+        <v>3.0454</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7647</v>
+        <v>-0.6706</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1468</v>
@@ -1468,13 +1468,13 @@
         <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0396</v>
+        <v>-0.1824</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3714</v>
+        <v>0.1345</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4111</v>
+        <v>-0.3169</v>
       </c>
       <c r="V13" t="n">
         <v>2.5659</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>2.379300000000001</v>
+        <v>1.5976</v>
       </c>
       <c r="E14" t="n">
-        <v>4.071400000000001</v>
+        <v>-6.4274</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6921</v>
+        <v>8.025399999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.805099999999999</v>
+        <v>-10.2145</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.6492</v>
+        <v>-12.4272</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1558</v>
+        <v>2.212799999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1747</v>
+        <v>-3.834899999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02760000000000007</v>
+        <v>-6.7215</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2025</v>
+        <v>2.8869</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.98</v>
+        <v>-6.3797</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.6215</v>
+        <v>-5.7055</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.3584</v>
+        <v>-0.6739999999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6828000000000002</v>
+        <v>20.7146</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.2029</v>
+        <v>-8.422499999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5197</v>
+        <v>29.1369</v>
       </c>
       <c r="S14" t="n">
-        <v>13.5943</v>
+        <v>2.8673</v>
       </c>
       <c r="T14" t="n">
-        <v>10.4857</v>
+        <v>1.156</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1086</v>
+        <v>1.711</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.7268</v>
+        <v>-11.7699</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6138</v>
+        <v>4.6735</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.3406</v>
+        <v>-16.4434</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.7387</v>
+        <v>-1.8917</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1571</v>
+        <v>-4.7418</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8958</v>
+        <v>2.8504</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2558</v>
+        <v>1.015599999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4935</v>
+        <v>-3.1781</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2378</v>
+        <v>4.1936</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6264999999999999</v>
+        <v>4.5514</v>
       </c>
       <c r="K15" t="n">
-        <v>1.379</v>
+        <v>-0.7044999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7524</v>
+        <v>5.2559</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3707</v>
+        <v>-3.5357</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1146</v>
+        <v>-2.4737</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4854</v>
+        <v>-1.062</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4552</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4553</v>
+        <v>-9.5608</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9105</v>
+        <v>6.8291</v>
       </c>
       <c r="S15" t="n">
-        <v>0.274</v>
+        <v>0.7562000000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4411</v>
+        <v>0.5678</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1671</v>
+        <v>0.1881</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.7237</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5447</v>
+        <v>-0.3006</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.2684</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.65</v>
+        <v>-2.1567</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.9022</v>
+        <v>0.8018</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2524</v>
+        <v>-2.9585</v>
       </c>
       <c r="G16" t="n">
-        <v>1.015599999999999</v>
+        <v>0.2558</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.1781</v>
+        <v>1.4935</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1936</v>
+        <v>-1.2378</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5514</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7044999999999999</v>
+        <v>1.379</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2559</v>
+        <v>-0.7524</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5357</v>
+        <v>-0.3707</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4737</v>
+        <v>0.1146</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.062</v>
+        <v>-0.4854</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.7316</v>
+        <v>0.4552</v>
       </c>
       <c r="Q16" t="n">
-        <v>-9.5608</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>6.8291</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.002400000000000263</v>
+        <v>-0.144</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4075</v>
+        <v>0.0858</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4099000000000001</v>
+        <v>-0.2298</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3006</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6311</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.3245</v>
+        <v>-3.3316</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7342</v>
+        <v>-1.6158</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5904</v>
+        <v>-1.7158</v>
       </c>
       <c r="G17" t="n">
         <v>-3.8355</v>
@@ -1780,13 +1780,13 @@
         <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1718</v>
+        <v>-0.1789</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2788</v>
+        <v>-0.1604</v>
       </c>
       <c r="U17" t="n">
-        <v>0.107</v>
+        <v>-0.01850000000000002</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.450199999999999</v>
+        <v>-5.1654</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.838599999999999</v>
+        <v>-2.471</v>
       </c>
       <c r="F18" t="n">
-        <v>4.388500000000001</v>
+        <v>-2.6945</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2919000000000003</v>
+        <v>-6.805099999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.008100000000001</v>
+        <v>-5.6492</v>
       </c>
       <c r="I18" t="n">
-        <v>7.3</v>
+        <v>-1.1558</v>
       </c>
       <c r="J18" t="n">
-        <v>20.4838</v>
+        <v>3.1747</v>
       </c>
       <c r="K18" t="n">
-        <v>2.218100000000001</v>
+        <v>-0.02760000000000007</v>
       </c>
       <c r="L18" t="n">
-        <v>18.2655</v>
+        <v>3.2025</v>
       </c>
       <c r="M18" t="n">
-        <v>-20.1916</v>
+        <v>-9.98</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.226000000000001</v>
+        <v>-5.6215</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.9657</v>
+        <v>-4.3584</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.642099999999999</v>
+        <v>-0.6828000000000002</v>
       </c>
       <c r="Q18" t="n">
-        <v>-44.3885</v>
+        <v>-13.2029</v>
       </c>
       <c r="R18" t="n">
-        <v>40.7461</v>
+        <v>12.5197</v>
       </c>
       <c r="S18" t="n">
-        <v>12.4854</v>
+        <v>6.049399999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>6.3736</v>
+        <v>3.9433</v>
       </c>
       <c r="U18" t="n">
-        <v>6.1117</v>
+        <v>2.1059</v>
       </c>
       <c r="V18" t="n">
-        <v>-12.5854</v>
+        <v>-3.7268</v>
       </c>
       <c r="W18" t="n">
-        <v>9.6922</v>
+        <v>3.6138</v>
       </c>
       <c r="X18" t="n">
-        <v>-22.2776</v>
+        <v>-7.3406</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.305</v>
+        <v>-7.113299999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.7956</v>
+        <v>-9.3172</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5094000000000001</v>
+        <v>2.2037</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.6488</v>
+        <v>3.127</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.0724</v>
+        <v>6.9991</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4237000000000003</v>
+        <v>-3.8722</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7668</v>
+        <v>4.3907</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2347</v>
+        <v>8.238299999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5323</v>
+        <v>-3.8474</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.415700000000001</v>
+        <v>-1.2638</v>
       </c>
       <c r="N19" t="n">
-        <v>-8.3071</v>
+        <v>-1.2391</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1086</v>
+        <v>-0.02469999999999997</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.4632</v>
+        <v>-9.7881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-17.983</v>
+        <v>-17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5197</v>
+        <v>7.5119</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1971</v>
+        <v>2.6586</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9402</v>
+        <v>1.3266</v>
       </c>
       <c r="U19" t="n">
-        <v>4.2568</v>
+        <v>1.3318</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.39</v>
+        <v>-3.1107</v>
       </c>
       <c r="W19" t="n">
-        <v>6.4803</v>
+        <v>2.2654</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.8703</v>
+        <v>-5.376</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.7334</v>
+        <v>-7.539300000000003</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.4041</v>
+        <v>-10.9319</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6706</v>
+        <v>3.3924</v>
       </c>
       <c r="G20" t="n">
-        <v>3.127</v>
+        <v>0.2919000000000003</v>
       </c>
       <c r="H20" t="n">
-        <v>6.9991</v>
+        <v>-7.008100000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.8722</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3907</v>
+        <v>20.4838</v>
       </c>
       <c r="K20" t="n">
-        <v>8.238299999999999</v>
+        <v>2.218100000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.8474</v>
+        <v>18.2655</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2638</v>
+        <v>-20.1916</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2391</v>
+        <v>-9.226000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.02469999999999997</v>
+        <v>-10.9657</v>
       </c>
       <c r="P20" t="n">
-        <v>-9.7881</v>
+        <v>-3.642099999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-17.3</v>
+        <v>-44.3885</v>
       </c>
       <c r="R20" t="n">
-        <v>7.5119</v>
+        <v>40.7461</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0384</v>
+        <v>8.3962</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2398</v>
+        <v>3.2806</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7986</v>
+        <v>5.1157</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.1107</v>
+        <v>-12.5854</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2654</v>
+        <v>9.6922</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.376</v>
+        <v>-22.2776</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.886099999999999</v>
+        <v>-9.2079</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.513199999999999</v>
+        <v>-6.1576</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.3727</v>
+        <v>-3.0502</v>
       </c>
       <c r="G21" t="n">
-        <v>4.9092</v>
+        <v>-4.6488</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6691</v>
+        <v>-5.0724</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2398999999999996</v>
+        <v>0.4237000000000003</v>
       </c>
       <c r="J21" t="n">
-        <v>17.9425</v>
+        <v>4.7668</v>
       </c>
       <c r="K21" t="n">
-        <v>11.8183</v>
+        <v>3.2347</v>
       </c>
       <c r="L21" t="n">
-        <v>6.1243</v>
+        <v>1.5323</v>
       </c>
       <c r="M21" t="n">
-        <v>-13.0337</v>
+        <v>-9.415700000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.1493</v>
+        <v>-8.3071</v>
       </c>
       <c r="O21" t="n">
-        <v>-5.8843</v>
+        <v>-1.1086</v>
       </c>
       <c r="P21" t="n">
-        <v>-13.6578</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q21" t="n">
-        <v>-32.3237</v>
+        <v>-17.983</v>
       </c>
       <c r="R21" t="n">
-        <v>18.6659</v>
+        <v>12.5197</v>
       </c>
       <c r="S21" t="n">
-        <v>-15.1427</v>
+        <v>2.2941</v>
       </c>
       <c r="T21" t="n">
-        <v>-8.463200000000001</v>
+        <v>0.5782</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.6792</v>
+        <v>1.716</v>
       </c>
       <c r="V21" t="n">
-        <v>14.0054</v>
+        <v>-1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>21.331</v>
+        <v>6.4803</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.3258</v>
+        <v>-7.8703</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.7622</v>
+        <v>-12.5927</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.168399999999998</v>
+        <v>-10.9479</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5941</v>
+        <v>-1.644800000000001</v>
       </c>
       <c r="G22" t="n">
         <v>13.9109</v>
@@ -2170,13 +2170,13 @@
         <v>28.4539</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4677</v>
+        <v>-2.2986</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3276000000000002</v>
+        <v>-2.4523</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7952</v>
+        <v>0.1538999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>3.110300000000001</v>
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>239.122</v>
+        <v>262.0090000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>169.1182</v>
+        <v>178.5277</v>
       </c>
       <c r="F23" t="n">
-        <v>70.0059</v>
+        <v>83.48149999999997</v>
       </c>
       <c r="G23" t="n">
         <v>176.751</v>
@@ -2245,19 +2245,19 @@
         <v>-517.8655</v>
       </c>
       <c r="R23" t="n">
-        <v>500.7912000000001</v>
+        <v>500.7912</v>
       </c>
       <c r="S23" t="n">
-        <v>9.790699999999998</v>
+        <v>32.677</v>
       </c>
       <c r="T23" t="n">
-        <v>-11.5414</v>
+        <v>-2.133100000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>21.33219999999999</v>
+        <v>34.8086</v>
       </c>
       <c r="V23" t="n">
-        <v>69.65419999999999</v>
+        <v>69.65420000000002</v>
       </c>
       <c r="W23" t="n">
         <v>309.3809</v>
